--- a/output/graficos_nacionales/plot_nacional_serie_i_ingr_s_2022.xlsx
+++ b/output/graficos_nacionales/plot_nacional_serie_i_ingr_s_2022.xlsx
@@ -72,7 +72,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-27 23:22</t>
+    <t xml:space="preserve">2026-10-05 18:55</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -564,7 +564,7 @@
         <v>12</v>
       </c>
       <c r="B12" s="2" t="n">
-        <v>1163774.62</v>
+        <v>1163774.63</v>
       </c>
     </row>
     <row r="13">
